--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,54 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132784602</v>
+        <v>137263673</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>75581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Döda granar, Gstr</t>
+          <t>Storsveden, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592271</v>
+        <v>592250</v>
       </c>
       <c r="R2" t="n">
-        <v>6710810</v>
+        <v>6710848</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,24 +775,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marita Grufvik</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marita Grufvik</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132784602</t>
+          <t>https://artportalen.se/Sighting/137263673</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132784615</v>
+        <v>132784602</v>
       </c>
       <c r="B3" t="n">
         <v>57972</v>
@@ -831,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -845,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592250</v>
+        <v>592271</v>
       </c>
       <c r="R3" t="n">
-        <v>6710834</v>
+        <v>6710810</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -916,13 +907,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132784615</t>
+          <t>https://artportalen.se/Sighting/132784602</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132784665</v>
+        <v>132784615</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
@@ -952,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -966,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592231</v>
+        <v>592250</v>
       </c>
       <c r="R4" t="n">
-        <v>6710876</v>
+        <v>6710834</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1037,13 +1028,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132784665</t>
+          <t>https://artportalen.se/Sighting/132784615</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132784707</v>
+        <v>132784665</v>
       </c>
       <c r="B5" t="n">
         <v>57972</v>
@@ -1073,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1087,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592172</v>
+        <v>592231</v>
       </c>
       <c r="R5" t="n">
-        <v>6710922</v>
+        <v>6710876</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1158,33 +1149,33 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132784707</t>
+          <t>https://artportalen.se/Sighting/132784665</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133238219</v>
+        <v>132784707</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1192,7 +1183,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1200,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knärot1, Gstr</t>
+          <t>Döda granar, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592231</v>
+        <v>592172</v>
       </c>
       <c r="R6" t="n">
-        <v>6710803</v>
+        <v>6710922</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,29 +1229,29 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1275,43 +1270,44 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133238219</t>
+          <t>https://artportalen.se/Sighting/132784707</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132784402</v>
+        <v>133238219</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,67 +1316,62 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592202</v>
+        <v>592231</v>
       </c>
       <c r="R7" t="n">
-        <v>6710809</v>
+        <v>6710803</v>
       </c>
       <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
         <v>1</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sandviken</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Årsunda</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1396,13 +1387,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132784402</t>
+          <t>https://artportalen.se/Sighting/133238219</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132785250</v>
+        <v>132784402</v>
       </c>
       <c r="B8" t="n">
         <v>99195</v>
@@ -1432,27 +1423,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Döda granar, Gstr</t>
+          <t>Knärot1, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592271</v>
+        <v>592202</v>
       </c>
       <c r="R8" t="n">
-        <v>6710810</v>
+        <v>6710809</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,6 +1488,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1517,7 +1508,249 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/132784402</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132785250</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Döda granar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>592271</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6710810</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marita Grufvik</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/132785250</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137263674</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storsveden, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>592253</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6710813</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Årsunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137263674</t>
         </is>
       </c>
     </row>
@@ -1530,6 +1763,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137263673</v>
       </c>
       <c r="B2" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137263673</v>
       </c>
       <c r="B2" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137263673</v>
       </c>
       <c r="B2" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137263673</v>
       </c>
       <c r="B2" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 12192-2026 artfynd.xlsx
+++ b/artfynd/A 12192-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137263673</v>
       </c>
       <c r="B2" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137263674</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
